--- a/backend/scripts/api_snapshot.xlsx
+++ b/backend/scripts/api_snapshot.xlsx
@@ -426,13 +426,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="53" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
@@ -673,18 +673,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>/api/storage/buckets</t>
+          <t>/api/stations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>List Buckets</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>List Active Solar Stations</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ดึงรายชื่อสถานีโซลาร์ฟาร์มทั้งหมด พร้อมข้อมูลกำลังผลิตจริงจากฐานข้อมูล</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>storage</t>
+          <t>stations</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -701,18 +705,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>/api/storage/buckets</t>
+          <t>/api/stations</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Create Bucket</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Create New Solar Station</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ลงทะเบียนสถานีโรงไฟฟ้าโซลาร์แห่งใหม่</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>storage</t>
+          <t>stations</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -724,23 +732,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>/api/storage/upload</t>
+          <t>/api/stations/archived</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Upload File</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>List Archived / Soft-Deleted Stations</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ดึงรายชื่อสถานีที่ถูกระงับการใช้งาน (Soft-deleted) ทั้งหมด</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>storage</t>
+          <t>stations</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -757,18 +769,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>/api/storage/download/{bucket_name}/{object_name}</t>
+          <t>/api/stations/nearest</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Download File</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Find Nearest Solar Station by Coordinates</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ค้นหาสถานีโซลาร์ฟาร์มที่อยู่ใกล้พิกัด Latitude/Longitude มากที่สุด (Nearest Mapping)</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>storage</t>
+          <t>stations</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -780,23 +796,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PUT</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>/api/storage/buckets/{bucket_name}/versioning</t>
+          <t>/api/stations/{station_id}</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Set Versioning</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Get Station Detail by ID</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ดึงข้อมูลรายละเอียดและสเปกของสถานีตาม ID พร้อมค่ากำลังผลิตล่าสุด</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>storage</t>
+          <t>stations</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -808,23 +828,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>PUT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>/api/label-studio/projects</t>
+          <t>/api/stations/{station_id}</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>List Projects</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Full Update Station Spec</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>อัปเดตข้อมูลสเปกของสถานีทั้งหมด (Full Update)</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>label-studio</t>
+          <t>stations</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -836,23 +860,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>/api/label-studio/projects</t>
+          <t>/api/stations/{station_id}</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Create Project</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Partial Update Station Spec</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>แก้ไขเฉพาะบางฟิลด์ของสถานี (Partial Update)</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>label-studio</t>
+          <t>stations</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -864,23 +892,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>/api/label-studio/projects/{project_id}/tasks</t>
+          <t>/api/stations/{station_id}</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>List Tasks</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Soft-Delete / Deactivate Station</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ปิดการใช้งานสถานีชั่วคราว (Soft-Delete) โดยไม่ลบประวัติใน DB</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>label-studio</t>
+          <t>stations</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -892,23 +924,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>PATCH</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>/api/label-studio/projects/{project_id}/tasks</t>
+          <t>/api/stations/{station_id}/restore</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Create Task</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Restore Soft-Deleted Station</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>กู้คืนสถานีที่เคยถูกระงับการใช้งานกลับมาทำงานใหม่ (Restore)</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>label-studio</t>
+          <t>stations</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -920,23 +956,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>/api/jobs/</t>
+          <t>/api/dashboard/summary</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Enqueue Job</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>System-wide Dashboard Overview (KPI Cards)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>สรุปภาพรวมทั้งระบบขึ้นหน้าแรก (KPI Cards, กำลังผลิตรวม, ความเสี่ยงรวม)</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -953,18 +993,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>/api/jobs/{job_id}</t>
+          <t>/api/dashboard/alerts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Get Job Status</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Real-time Alert Feeds for Critical / Warning Stations</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ดึงรายการแจ้งเตือนด่วน (Real-time Alert Feeds) ที่ต้องการเฝ้าระวังหรือเร่งสำรองไฟ</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -981,25 +1025,1161 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>/api/dashboard/grafana-links</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Get Observability Grafana Dashboard Links</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ดึง URL สำหรับ Embed หรือเปิดดู Grafana Dashboards</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>/api/dashboard/station/{station_id}</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Station-Specific Dashboard Detail (Forecast Curve + Cloud Trend)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ดึงข้อมูลแดชบอร์ดเฉพาะสถานี (กราฟพยากรณ์ 3 ชม., ทัศนวิสัยเมฆ, คำแนะนำ ΔP)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>dashboard</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>/api/storage/buckets</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>List Buckets</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>/api/storage/buckets</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Create Bucket</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>/api/storage/upload</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Upload File</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>/api/storage/download/{bucket_name}/{object_name}</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Download File</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PUT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>/api/storage/buckets/{bucket_name}/versioning</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Set Versioning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>storage</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>/api/label-studio/projects</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>List Projects</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>label-studio</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>/api/label-studio/projects</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Create Project</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>label-studio</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>/api/label-studio/projects/{project_id}/tasks</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>List Tasks</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>label-studio</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>/api/label-studio/projects/{project_id}/tasks</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Create Task</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>label-studio</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>/api/label-studio/projects/{project_id}/tasks/{task_id}/annotations</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>List Annotations</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>label-studio</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>/api/label-studio/projects/{project_id}/tasks/{task_id}/annotations</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Create Annotation</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>label-studio</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>/api/label-studio/ground-truth/submit</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Submit Ground Truth</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ส่ง GHI จริง 1 ค่า -&gt; Label Studio (สร้าง/อัปเดต) -&gt; นัด retrain.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>label-studio</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>/api/label-studio/ground-truth/batch-submit</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Batch Submit Ground Truth</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ส่ง GHI จริงหลายค่า (จากตารางหน้าเว็บ).</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>label-studio</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>/api/label-studio/ground-truth/upload/preview</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Preview Ground Truth File</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>อ่านหัวตาราง + ตัวอย่างแถวของไฟล์ และเดาคอลัมน์เวลา/GHI ให้ผู้ใช้เลือกยืนยัน.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>label-studio</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>/api/label-studio/ground-truth/upload</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Upload Ground Truth File</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>นำเข้า GHI จริงจากไฟล์ CSV/XLSX เฉพาะแถวที่อยู่ในวันที่เลือก (เวลาไทย) ตามคอลัมน์ที่ผู้ใช้ระบุ.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>label-studio</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>/api/jobs/queues</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Summary of All Redis Task Queues</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>สรุปภาพรวมของทุกคิวใน Redis (จำนวนงานที่รอ, กำลังรัน, พัง)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>/api/jobs/queues/{name}/jobs</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>List Pending Jobs in a Specific Queue</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ดูรายการ Job ทั้งหมดที่ค้างอยู่ในคิวที่เลือก</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>/api/jobs/queues/{name}/clear</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Clear / Flush All Pending Jobs in a Queue</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ล้างคิวงานทั้งหมด (Flush Pending Jobs)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>/api/jobs/{job_id}/retry</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Retry a Failed Job</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>สั่งให้ Job ที่เคย Failed รันใหม่อีกครั้ง</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>/api/jobs/{job_id}</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Get Job Status and Result</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>/api/jobs/{job_id}</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Cancel / Remove Job from Queue</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>ยกเลิก / ลบ Job ออกจากคิวทันท่วงที (Cancel Job)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>jobs</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>/api/inference/predict</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Enqueue 3-Hour Solar Forecast Request</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>สั่งคำขอพยากรณ์ไฟฟ้าล่วงหน้า 3 ชม. (Enqueue to inference_queue)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>/api/inference/result/{job_id}</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Get Forecast Result by Job ID</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ดึงผลลัพธ์การพยากรณ์เมื่อ Worker ประมวลผลเสร็จ</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>/api/inference/latest/{station_id}</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Get Latest Pre-computed Forecast for Station Dashboard</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ดึงผลการพยากรณ์รอบล่าสุดของสถานีขึ้นแสดงบน Dashboard ทันที</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>/api/inference/history/{station_id}</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Get Historical Forecasts for Comparison</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ดึงประวัติผลพยากรณ์ย้อนหลังเพื่อนำไปพลอตกราฟเปรียบเทียบ</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>/api/inference/predictions-by-date</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Forecasts of a day aligned to real time, with ground-truth labels</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ค่าพยากรณ์ + GHI จาก weather_history ของวันที่เลือก (เรียงตามเวลาจริง) + ค่าจริงที่ label ไว้แล้ว สำหรับหน้า labeling.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>/api/ingestion/trigger</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Trigger Real-time Weather &amp; Satellite Ingestion</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>สั่งดึงข้อมูลสภาพอากาศแบบ Real-time (Open-Meteo) และภาพดาวเทียม Himawari (NICT) เข้าสู่ระบบทันที</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>ingestion</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>/api/ingestion/catchup</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Trigger Auto Catch-up / Gap Backfill for Station</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>สั่งตรวจสอบ Gap ของข้อมูลและดึงข้อมูลย้อนหลังทั้ง Weather Time-Series และภาพถ่ายดาวเทียม 12 เฟรมอัตโนมัติ</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>ingestion</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>/api/ingestion/weather/{station_id}/recent</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Get Normalized Weather Time-series for Station</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ดึงข้อมูลสภาพอากาศย้อนหลังระดับ Canonical Schema เพื่อใช้เป็น Input สำหรับโมเดล LSTM</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>ingestion</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>/api/ingestion/satellite/{station_id}/frames</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Get Recent Satellite Frame Sequences</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ดึงประวัติ URL ภาพถ่ายดาวเทียม Himawari ล่าสุดเพื่อใช้ส่งให้ ConvLSTM Cloud Motion Model</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>ingestion</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>/api/ingestion/status</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Get Ingestion Health &amp; Metrics</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ตรวจสอบสถานะสุขภาพและการเชื่อมต่อ Data Source (Open-Meteo, NICT Himawari) และจำนวนข้อมูลในระบบ</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ingestion</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>/api/ingestion/satellite/{station_id}/latest.png</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Newest real satellite crop around a station (PNG)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ภาพดาวเทียมจริงล่าสุดรอบสถานี (true-colour 64x64 พิกเซล) ที่ inference worker เก็บไว้ใน MinIO.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>ingestion</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>/api/frame-review/frames</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>List Frames</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Real daytime satellite frames of one station and day, with automatic hints and the saved reviews.</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>frame-review</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>/api/frame-review/frames</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Submit Reviews</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Save the reviewer's verdicts. Rejected frames are left out of the next ConvLSTM retrain.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>frame-review</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>/api/frame-review/status</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Convlstm Status</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Batch counter of new satellite scans, the deployed ConvLSTM and the result of the last retrain.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>frame-review</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>/health</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>Health Check</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>ตรวจสอบว่า API server ทำงานปกติ</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/backend/scripts/api_snapshot.xlsx
+++ b/backend/scripts/api_snapshot.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1851,7 +1851,8 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ค่าพยากรณ์ + GHI จาก weather_history ของวันที่เลือก (เรียงตามเวลาจริง) + ค่าจริงที่ label ไว้แล้ว สำหรับหน้า labeling.</t>
+          <t>ค่าพยากรณ์ + GHI จาก weather_history ของวันที่เลือก (เรียงตามเวลาจริง) + ค่าจริงที่ label ไว้แล้ว
+ใช้ทั้งหน้า labeling (predicted_ghi = รอบล่าสุด) และกราฟทั้งวันของหน้าพยากรณ์ (forecast_* ตาม lead_minutes).</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2065,22 +2066,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>/api/frame-review/frames</t>
+          <t>/api/ingestion/satellite/{station_id}/day-frames</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>List Frames</t>
+          <t>Real satellite frames of a day and the newest ConvLSTM forecast frames</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Real daytime satellite frames of one station and day, with automatic hints and the saved reviews.</t>
+          <t>Real Band 03 frames of one station and day, and for today the frames the ConvLSTM predicted in the newest round.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>frame-review</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2092,7 +2093,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2102,12 +2103,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Submit Reviews</t>
+          <t>List Frames</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Save the reviewer's verdicts. Rejected frames are left out of the next ConvLSTM retrain.</t>
+          <t>Real daytime satellite frames of one station and day, with automatic hints and the saved reviews.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2124,22 +2125,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>/api/frame-review/status</t>
+          <t>/api/frame-review/frames</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Convlstm Status</t>
+          <t>Submit Reviews</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Batch counter of new satellite scans, the deployed ConvLSTM and the result of the last retrain.</t>
+          <t>Save the reviewer's verdicts. Rejected frames are left out of the next ConvLSTM retrain.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2161,25 +2162,89 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>/api/frame-review/status</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Convlstm Status</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Batch counter of new satellite scans, the deployed ConvLSTM and the result of the last retrain.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>frame-review</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>/api/retrain/status</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Deployed models, pending retrains and the retrain history of both models</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Deployed versions, what is pending and the retrain history of the LSTM and the ConvLSTM.</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>retrain</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>/health</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>Health Check</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>ตรวจสอบว่า API server ทำงานปกติ</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/backend/scripts/api_snapshot.xlsx
+++ b/backend/scripts/api_snapshot.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1392,22 +1392,22 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>/api/label-studio/ground-truth/submit</t>
+          <t>/api/label-studio/ground-truth/calibration-status</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Submit Ground Truth</t>
+          <t>Has the satellite relation been compared with measured GHI of this station?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ส่ง GHI จริง 1 ค่า -&gt; Label Studio (สร้าง/อัปเดต) -&gt; นัด retrain.</t>
+          <t>สูตรแสงจากภาพดาวเทียมเทียบกับค่าวัดจริงของสถานีนี้แล้วหรือยัง (ผลของงาน check_satellite_calibration ที่รันเองหลังบันทึกค่าวัดจริง).</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>/api/label-studio/ground-truth/batch-submit</t>
+          <t>/api/label-studio/ground-truth/submit</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Batch Submit Ground Truth</t>
+          <t>Submit Ground Truth</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ส่ง GHI จริงหลายค่า (จากตารางหน้าเว็บ).</t>
+          <t>ส่ง GHI จริง 1 ค่า -&gt; Label Studio (สร้าง/อัปเดต) -&gt; นัด retrain.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>/api/label-studio/ground-truth/upload/preview</t>
+          <t>/api/label-studio/ground-truth/batch-submit</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Preview Ground Truth File</t>
+          <t>Batch Submit Ground Truth</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>อ่านหัวตาราง + ตัวอย่างแถวของไฟล์ และเดาคอลัมน์เวลา/GHI ให้ผู้ใช้เลือกยืนยัน.</t>
+          <t>ส่ง GHI จริงหลายค่า (จากตารางหน้าเว็บ).</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1493,17 +1493,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>/api/label-studio/ground-truth/upload</t>
+          <t>/api/label-studio/ground-truth/upload/preview</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Upload Ground Truth File</t>
+          <t>Preview Ground Truth File</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>นำเข้า GHI จริงจากไฟล์ CSV/XLSX เฉพาะแถวที่อยู่ในวันที่เลือก (เวลาไทย) ตามคอลัมน์ที่ผู้ใช้ระบุ.</t>
+          <t>อ่านหัวตาราง + ตัวอย่างแถวของไฟล์ และเดาคอลัมน์เวลา/GHI ให้ผู้ใช้เลือกยืนยัน.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1520,27 +1520,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>/api/jobs/queues</t>
+          <t>/api/label-studio/ground-truth/upload</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Summary of All Redis Task Queues</t>
+          <t>Upload Ground Truth File</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>สรุปภาพรวมของทุกคิวใน Redis (จำนวนงานที่รอ, กำลังรัน, พัง)</t>
+          <t>นำเข้า GHI จริงจากไฟล์ CSV/XLSX เฉพาะแถวที่อยู่ในวันที่เลือก (เวลาไทย) ตามคอลัมน์ที่ผู้ใช้ระบุ.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>jobs</t>
+          <t>label-studio</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1557,17 +1557,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>/api/jobs/queues/{name}/jobs</t>
+          <t>/api/jobs/queues</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>List Pending Jobs in a Specific Queue</t>
+          <t>Summary of All Redis Task Queues</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ดูรายการ Job ทั้งหมดที่ค้างอยู่ในคิวที่เลือก</t>
+          <t>สรุปภาพรวมของทุกคิวใน Redis (จำนวนงานที่รอ, กำลังรัน, พัง)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1584,22 +1584,22 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>/api/jobs/queues/{name}/clear</t>
+          <t>/api/jobs/queues/{name}/jobs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Clear / Flush All Pending Jobs in a Queue</t>
+          <t>List Pending Jobs in a Specific Queue</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ล้างคิวงานทั้งหมด (Flush Pending Jobs)</t>
+          <t>ดูรายการ Job ทั้งหมดที่ค้างอยู่ในคิวที่เลือก</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1616,22 +1616,22 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>/api/jobs/{job_id}/retry</t>
+          <t>/api/jobs/queues/{name}/clear</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Retry a Failed Job</t>
+          <t>Clear / Flush All Pending Jobs in a Queue</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>สั่งให้ Job ที่เคย Failed รันใหม่อีกครั้ง</t>
+          <t>ล้างคิวงานทั้งหมด (Flush Pending Jobs)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1648,20 +1648,24 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>/api/jobs/{job_id}</t>
+          <t>/api/jobs/{job_id}/retry</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Get Job Status and Result</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Retry a Failed Job</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>สั่งให้ Job ที่เคย Failed รันใหม่อีกครั้ง</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>jobs</t>
@@ -1676,7 +1680,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DELETE</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1686,14 +1690,10 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cancel / Remove Job from Queue</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ยกเลิก / ลบ Job ออกจากคิวทันท่วงที (Cancel Job)</t>
-        </is>
-      </c>
+          <t>Get Job Status and Result</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>jobs</t>
@@ -1708,27 +1708,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>DELETE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>/api/inference/predict</t>
+          <t>/api/jobs/{job_id}</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Enqueue 3-Hour Solar Forecast Request</t>
+          <t>Cancel / Remove Job from Queue</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>สั่งคำขอพยากรณ์ไฟฟ้าล่วงหน้า 3 ชม. (Enqueue to inference_queue)</t>
+          <t>ยกเลิก / ลบ Job ออกจากคิวทันท่วงที (Cancel Job)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>inference</t>
+          <t>jobs</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1740,22 +1740,22 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>/api/inference/result/{job_id}</t>
+          <t>/api/inference/predict</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Get Forecast Result by Job ID</t>
+          <t>Enqueue 3-Hour Solar Forecast Request</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ดึงผลลัพธ์การพยากรณ์เมื่อ Worker ประมวลผลเสร็จ</t>
+          <t>สั่งคำขอพยากรณ์ไฟฟ้าล่วงหน้า 3 ชม. (Enqueue to inference_queue)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -1777,17 +1777,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>/api/inference/latest/{station_id}</t>
+          <t>/api/inference/result/{job_id}</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Get Latest Pre-computed Forecast for Station Dashboard</t>
+          <t>Get Forecast Result by Job ID</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ดึงผลการพยากรณ์รอบล่าสุดของสถานีขึ้นแสดงบน Dashboard ทันที</t>
+          <t>ดึงผลลัพธ์การพยากรณ์เมื่อ Worker ประมวลผลเสร็จ</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1809,17 +1809,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>/api/inference/history/{station_id}</t>
+          <t>/api/inference/latest/{station_id}</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Get Historical Forecasts for Comparison</t>
+          <t>Get Latest Pre-computed Forecast for Station Dashboard</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ดึงประวัติผลพยากรณ์ย้อนหลังเพื่อนำไปพลอตกราฟเปรียบเทียบ</t>
+          <t>ดึงผลการพยากรณ์รอบล่าสุดของสถานีขึ้นแสดงบน Dashboard ทันที</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -1841,55 +1841,55 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>/api/inference/history/{station_id}</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Get Historical Forecasts for Comparison</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ดึงประวัติผลพยากรณ์ย้อนหลังเพื่อนำไปพลอตกราฟเปรียบเทียบ</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>inference</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>/api/inference/predictions-by-date</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Forecasts of a day aligned to real time, with ground-truth labels</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>ค่าพยากรณ์ + GHI จาก weather_history ของวันที่เลือก (เรียงตามเวลาจริง) + ค่าจริงที่ label ไว้แล้ว
 ใช้ทั้งหน้า labeling (predicted_ghi = รอบล่าสุด) และกราฟทั้งวันของหน้าพยากรณ์ (forecast_* ตาม lead_minutes).</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>inference</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>/api/ingestion/trigger</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Trigger Real-time Weather &amp; Satellite Ingestion</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>สั่งดึงข้อมูลสภาพอากาศแบบ Real-time (Open-Meteo) และภาพดาวเทียม Himawari (NICT) เข้าสู่ระบบทันที</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>ingestion</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -1906,17 +1906,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>/api/ingestion/catchup</t>
+          <t>/api/ingestion/trigger</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Trigger Auto Catch-up / Gap Backfill for Station</t>
+          <t>Trigger Real-time Weather &amp; Satellite Ingestion</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>สั่งตรวจสอบ Gap ของข้อมูลและดึงข้อมูลย้อนหลังทั้ง Weather Time-Series และภาพถ่ายดาวเทียม 12 เฟรมอัตโนมัติ</t>
+          <t>สั่งดึงข้อมูลสภาพอากาศแบบ Real-time (Open-Meteo) และภาพดาวเทียม Himawari (NICT) เข้าสู่ระบบทันที</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1933,22 +1933,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>/api/ingestion/weather/{station_id}/recent</t>
+          <t>/api/ingestion/catchup</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Get Normalized Weather Time-series for Station</t>
+          <t>Trigger Auto Catch-up / Gap Backfill for Station</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ดึงข้อมูลสภาพอากาศย้อนหลังระดับ Canonical Schema เพื่อใช้เป็น Input สำหรับโมเดล LSTM</t>
+          <t>สั่งตรวจสอบ Gap ของข้อมูลและดึงข้อมูลย้อนหลังทั้ง Weather Time-Series และภาพถ่ายดาวเทียม 12 เฟรมอัตโนมัติ</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1970,17 +1970,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>/api/ingestion/satellite/{station_id}/frames</t>
+          <t>/api/ingestion/weather/{station_id}/recent</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Get Recent Satellite Frame Sequences</t>
+          <t>Get Normalized Weather Time-series for Station</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ดึงประวัติ URL ภาพถ่ายดาวเทียม Himawari ล่าสุดเพื่อใช้ส่งให้ ConvLSTM Cloud Motion Model</t>
+          <t>ดึงข้อมูลสภาพอากาศย้อนหลังระดับ Canonical Schema เพื่อใช้เป็น Input สำหรับโมเดล LSTM</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2002,17 +2002,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>/api/ingestion/status</t>
+          <t>/api/ingestion/satellite/{station_id}/frames</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Get Ingestion Health &amp; Metrics</t>
+          <t>Get Recent Satellite Frame Sequences</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ตรวจสอบสถานะสุขภาพและการเชื่อมต่อ Data Source (Open-Meteo, NICT Himawari) และจำนวนข้อมูลในระบบ</t>
+          <t>ดึงประวัติ URL ภาพถ่ายดาวเทียม Himawari ล่าสุดเพื่อใช้ส่งให้ ConvLSTM Cloud Motion Model</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2034,17 +2034,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>/api/ingestion/satellite/{station_id}/latest.png</t>
+          <t>/api/ingestion/status</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Newest real satellite crop around a station (PNG)</t>
+          <t>Get Ingestion Health &amp; Metrics</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ภาพดาวเทียมจริงล่าสุดรอบสถานี (true-colour 64x64 พิกเซล) ที่ inference worker เก็บไว้ใน MinIO.</t>
+          <t>ตรวจสอบสถานะสุขภาพและการเชื่อมต่อ Data Source (Open-Meteo, NICT Himawari) และจำนวนข้อมูลในระบบ</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>/api/ingestion/satellite/{station_id}/day-frames</t>
+          <t>/api/ingestion/satellite/{station_id}/latest.png</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Real satellite frames of a day and the newest ConvLSTM forecast frames</t>
+          <t>Newest real satellite crop around a station (PNG)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Real Band 03 frames of one station and day, and for today the frames the ConvLSTM predicted in the newest round.</t>
+          <t>ภาพดาวเทียมจริงล่าสุดรอบสถานี (true-colour 64x64 พิกเซล) ที่ inference worker เก็บไว้ใน MinIO.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2098,22 +2098,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>/api/frame-review/frames</t>
+          <t>/api/ingestion/satellite/{station_id}/day-frames</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>List Frames</t>
+          <t>Real satellite frames of a day and the newest ConvLSTM forecast frames</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Real daytime satellite frames of one station and day, with automatic hints and the saved reviews.</t>
+          <t>Real Band 03 frames of one station and day, and for today the frames the ConvLSTM predicted in the newest round.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>frame-review</t>
+          <t>ingestion</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2125,7 +2125,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Submit Reviews</t>
+          <t>List Frames</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Save the reviewer's verdicts. Rejected frames are left out of the next ConvLSTM retrain.</t>
+          <t>Real daytime satellite frames of one station and day, with automatic hints and the saved reviews.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2157,22 +2157,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>/api/frame-review/status</t>
+          <t>/api/frame-review/frames</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Convlstm Status</t>
+          <t>Submit Reviews</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Batch counter of new satellite scans, the deployed ConvLSTM and the result of the last retrain.</t>
+          <t>Save the reviewer's verdicts. Rejected frames are left out of the next ConvLSTM retrain.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2194,22 +2194,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>/api/retrain/status</t>
+          <t>/api/frame-review/status</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Deployed models, pending retrains and the retrain history of both models</t>
+          <t>Convlstm Status</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Deployed versions, what is pending and the retrain history of the LSTM and the ConvLSTM.</t>
+          <t>Batch counter of new satellite scans, the deployed ConvLSTM and the result of the last retrain.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>retrain</t>
+          <t>frame-review</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2226,25 +2226,89 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>/api/retrain/status</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Deployed models, pending retrains and the retrain history of both models</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Deployed versions, what is pending and the retrain history of the LSTM and the ConvLSTM.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>retrain</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>/api/retrain/runs/{run_id}/curves</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Per-epoch learning curves of one retrain run</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Learning curves of one retrain run: training loss, validation metric and learning rate per epoch.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>retrain</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>/health</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>Health Check</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>ตรวจสอบว่า API server ทำงานปกติ</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>system</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/backend/scripts/api_snapshot.xlsx
+++ b/backend/scripts/api_snapshot.xlsx
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>สรุปภาพรวมของทุกคิวใน Redis (จำนวนงานที่รอ, กำลังรัน, พัง)</t>
+          <t>สรุปจำนวนงานที่รอในแต่ละคิวของ Redis</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">

--- a/backend/scripts/api_snapshot.xlsx
+++ b/backend/scripts/api_snapshot.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1906,17 +1906,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>/api/ingestion/trigger</t>
+          <t>/api/ingestion/catchup</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Trigger Real-time Weather &amp; Satellite Ingestion</t>
+          <t>Trigger Auto Catch-up / Gap Backfill for Station</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>สั่งดึงข้อมูลสภาพอากาศแบบ Real-time (Open-Meteo) และภาพดาวเทียม Himawari (NICT) เข้าสู่ระบบทันที</t>
+          <t>สั่งตรวจสอบ Gap ของข้อมูลและดึงข้อมูลย้อนหลังทั้ง Weather Time-Series และภาพถ่ายดาวเทียม 12 เฟรมอัตโนมัติ</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1933,22 +1933,22 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>/api/ingestion/catchup</t>
+          <t>/api/ingestion/weather/{station_id}/recent</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Trigger Auto Catch-up / Gap Backfill for Station</t>
+          <t>Get Normalized Weather Time-series for Station</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>สั่งตรวจสอบ Gap ของข้อมูลและดึงข้อมูลย้อนหลังทั้ง Weather Time-Series และภาพถ่ายดาวเทียม 12 เฟรมอัตโนมัติ</t>
+          <t>ดึงข้อมูลสภาพอากาศย้อนหลังระดับ Canonical Schema เพื่อใช้เป็น Input สำหรับโมเดล LSTM</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -1970,17 +1970,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>/api/ingestion/weather/{station_id}/recent</t>
+          <t>/api/ingestion/satellite/{station_id}/frames</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Get Normalized Weather Time-series for Station</t>
+          <t>Get Recent Satellite Frame Sequences</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ดึงข้อมูลสภาพอากาศย้อนหลังระดับ Canonical Schema เพื่อใช้เป็น Input สำหรับโมเดล LSTM</t>
+          <t>ดึงประวัติ URL ภาพถ่ายดาวเทียม Himawari ล่าสุดเพื่อใช้ส่งให้ ConvLSTM Cloud Motion Model</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2002,17 +2002,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>/api/ingestion/satellite/{station_id}/frames</t>
+          <t>/api/ingestion/status</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Get Recent Satellite Frame Sequences</t>
+          <t>Get Ingestion Health &amp; Metrics</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ดึงประวัติ URL ภาพถ่ายดาวเทียม Himawari ล่าสุดเพื่อใช้ส่งให้ ConvLSTM Cloud Motion Model</t>
+          <t>ตรวจสอบสถานะสุขภาพและการเชื่อมต่อ Data Source (Open-Meteo, NICT Himawari) และจำนวนข้อมูลในระบบ</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2034,17 +2034,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>/api/ingestion/status</t>
+          <t>/api/ingestion/satellite/{station_id}/latest.png</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Get Ingestion Health &amp; Metrics</t>
+          <t>Newest real satellite crop around a station (PNG)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ตรวจสอบสถานะสุขภาพและการเชื่อมต่อ Data Source (Open-Meteo, NICT Himawari) และจำนวนข้อมูลในระบบ</t>
+          <t>ภาพดาวเทียมจริงล่าสุดรอบสถานี (true-colour 64x64 พิกเซล) ที่ inference worker เก็บไว้ใน MinIO.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>/api/ingestion/satellite/{station_id}/latest.png</t>
+          <t>/api/ingestion/satellite/{station_id}/day-frames</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newest real satellite crop around a station (PNG)</t>
+          <t>Real satellite frames of a day and the newest ConvLSTM forecast frames</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ภาพดาวเทียมจริงล่าสุดรอบสถานี (true-colour 64x64 พิกเซล) ที่ inference worker เก็บไว้ใน MinIO.</t>
+          <t>Real Band 03 frames of one station and day, and for today the frames the ConvLSTM predicted in the newest round.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2098,22 +2098,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>/api/ingestion/satellite/{station_id}/day-frames</t>
+          <t>/api/frame-review/frames</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Real satellite frames of a day and the newest ConvLSTM forecast frames</t>
+          <t>List Frames</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Real Band 03 frames of one station and day, and for today the frames the ConvLSTM predicted in the newest round.</t>
+          <t>Real daytime satellite frames of one station and day, with automatic hints and the saved reviews.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ingestion</t>
+          <t>frame-review</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2125,7 +2125,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>List Frames</t>
+          <t>Submit Reviews</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Real daytime satellite frames of one station and day, with automatic hints and the saved reviews.</t>
+          <t>Save the reviewer's verdicts. Rejected frames are left out of the next ConvLSTM retrain.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2157,22 +2157,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>/api/frame-review/frames</t>
+          <t>/api/frame-review/status</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Submit Reviews</t>
+          <t>Convlstm Status</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Save the reviewer's verdicts. Rejected frames are left out of the next ConvLSTM retrain.</t>
+          <t>Batch counter of new satellite scans, the deployed ConvLSTM and the result of the last retrain.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2194,22 +2194,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>/api/frame-review/status</t>
+          <t>/api/retrain/status</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Convlstm Status</t>
+          <t>Deployed models, pending retrains and the retrain history of both models</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Batch counter of new satellite scans, the deployed ConvLSTM and the result of the last retrain.</t>
+          <t>Deployed versions, what is pending and the retrain history of the LSTM and the ConvLSTM.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>frame-review</t>
+          <t>retrain</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2226,17 +2226,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>/api/retrain/status</t>
+          <t>/api/retrain/runs/{run_id}/curves</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Deployed models, pending retrains and the retrain history of both models</t>
+          <t>Per-epoch learning curves of one retrain run</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Deployed versions, what is pending and the retrain history of the LSTM and the ConvLSTM.</t>
+          <t>Learning curves of one retrain run: training loss, validation metric and learning rate per epoch.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2258,57 +2258,25 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>/api/retrain/runs/{run_id}/curves</t>
+          <t>/health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Per-epoch learning curves of one retrain run</t>
+          <t>Health Check</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Learning curves of one retrain run: training loss, validation metric and learning rate per epoch.</t>
+          <t>ตรวจสอบว่า API server ทำงานปกติ</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>retrain</t>
+          <t>system</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>/health</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Health Check</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>ตรวจสอบว่า API server ทำงานปกติ</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>system</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
         <is>
           <t>No</t>
         </is>
